--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.63464</v>
+        <v>17.14624</v>
       </c>
       <c r="D2" t="n">
-        <v>16.43217</v>
+        <v>16.42838</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82962</v>
+        <v>16.63315</v>
       </c>
       <c r="F2" t="n">
-        <v>42.59363</v>
+        <v>42.48691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05109</v>
+        <v>0.04965</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79782</v>
+        <v>1.80644</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8651</v>
+        <v>16.9637</v>
       </c>
       <c r="D3" t="n">
-        <v>16.66901</v>
+        <v>16.34412</v>
       </c>
       <c r="E3" t="n">
-        <v>16.25184</v>
+        <v>16.56496</v>
       </c>
       <c r="F3" t="n">
-        <v>41.89078</v>
+        <v>42.03432</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05054</v>
+        <v>0.05039</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80276</v>
+        <v>1.79902</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.44459</v>
+        <v>16.8725</v>
       </c>
       <c r="D4" t="n">
-        <v>16.87111</v>
+        <v>16.38147</v>
       </c>
       <c r="E4" t="n">
-        <v>16.47476</v>
+        <v>16.8111</v>
       </c>
       <c r="F4" t="n">
-        <v>42.0297</v>
+        <v>43.08043</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05149</v>
+        <v>0.05018</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78931</v>
+        <v>1.82213</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.48929</v>
+        <v>16.67993</v>
       </c>
       <c r="D6" t="n">
-        <v>15.53748</v>
+        <v>16.1388</v>
       </c>
       <c r="E6" t="n">
-        <v>16.17387</v>
+        <v>16.48551</v>
       </c>
       <c r="F6" t="n">
-        <v>21.70722</v>
+        <v>21.68451</v>
       </c>
       <c r="G6" t="n">
-        <v>33.73546</v>
+        <v>34.24838</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.88824</v>
+        <v>16.57094</v>
       </c>
       <c r="D7" t="n">
-        <v>15.95202</v>
+        <v>15.63742</v>
       </c>
       <c r="E7" t="n">
-        <v>16.02428</v>
+        <v>16.49717</v>
       </c>
       <c r="F7" t="n">
-        <v>21.66345</v>
+        <v>22.0905</v>
       </c>
       <c r="G7" t="n">
-        <v>34.24098</v>
+        <v>33.62455</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.68106</v>
+        <v>16.40457</v>
       </c>
       <c r="D8" t="n">
-        <v>15.76522</v>
+        <v>15.85693</v>
       </c>
       <c r="E8" t="n">
-        <v>16.34622</v>
+        <v>15.98622</v>
       </c>
       <c r="F8" t="n">
-        <v>21.83892</v>
+        <v>22.54503</v>
       </c>
       <c r="G8" t="n">
-        <v>33.46908</v>
+        <v>34.746</v>
       </c>
     </row>
   </sheetData>
